--- a/students.xlsx
+++ b/students.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\endoimage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD414E0-6637-4CEF-81D9-791415D64D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BC2DDF-9046-4B6A-8186-7C63307D84C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="98">
   <si>
     <t>강승훈</t>
   </si>
@@ -324,6 +324,18 @@
   </si>
   <si>
     <t>6조</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>조</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>교번</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -705,18 +717,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" thickBot="1">
@@ -724,10 +736,10 @@
         <v>89</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" thickBot="1">
@@ -735,10 +747,10 @@
         <v>89</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" thickBot="1">
@@ -746,10 +758,10 @@
         <v>89</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" thickBot="1">
@@ -757,10 +769,10 @@
         <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" thickBot="1">
@@ -768,10 +780,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" thickBot="1">
@@ -779,10 +791,10 @@
         <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" thickBot="1">
@@ -790,10 +802,10 @@
         <v>89</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" thickBot="1">
@@ -801,21 +813,21 @@
         <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" thickBot="1">
       <c r="A10" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="1">
-        <v>10</v>
+      <c r="B10" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" thickBot="1">
@@ -823,10 +835,10 @@
         <v>89</v>
       </c>
       <c r="B11" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" thickBot="1">
@@ -834,10 +846,10 @@
         <v>89</v>
       </c>
       <c r="B12" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18" thickBot="1">
@@ -845,10 +857,10 @@
         <v>89</v>
       </c>
       <c r="B13" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18" thickBot="1">
@@ -856,21 +868,21 @@
         <v>89</v>
       </c>
       <c r="B14" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" thickBot="1">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" thickBot="1">
@@ -878,10 +890,10 @@
         <v>90</v>
       </c>
       <c r="B16" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18" thickBot="1">
@@ -889,10 +901,10 @@
         <v>90</v>
       </c>
       <c r="B17" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18" thickBot="1">
@@ -900,10 +912,10 @@
         <v>90</v>
       </c>
       <c r="B18" s="1">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18" thickBot="1">
@@ -911,10 +923,10 @@
         <v>90</v>
       </c>
       <c r="B19" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" thickBot="1">
@@ -922,10 +934,10 @@
         <v>90</v>
       </c>
       <c r="B20" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18" thickBot="1">
@@ -933,10 +945,10 @@
         <v>90</v>
       </c>
       <c r="B21" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18" thickBot="1">
@@ -944,10 +956,10 @@
         <v>90</v>
       </c>
       <c r="B22" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18" thickBot="1">
@@ -955,10 +967,10 @@
         <v>90</v>
       </c>
       <c r="B23" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" thickBot="1">
@@ -966,10 +978,10 @@
         <v>90</v>
       </c>
       <c r="B24" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="18" thickBot="1">
@@ -977,10 +989,10 @@
         <v>90</v>
       </c>
       <c r="B25" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="18" thickBot="1">
@@ -988,10 +1000,10 @@
         <v>90</v>
       </c>
       <c r="B26" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" thickBot="1">
@@ -999,10 +1011,10 @@
         <v>90</v>
       </c>
       <c r="B27" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="18" thickBot="1">
@@ -1010,21 +1022,21 @@
         <v>90</v>
       </c>
       <c r="B28" s="1">
-        <v>28</v>
-      </c>
-      <c r="C28" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" thickBot="1">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" s="1">
-        <v>29</v>
-      </c>
-      <c r="C29" s="4" t="s">
         <v>28</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="18" thickBot="1">
@@ -1032,10 +1044,10 @@
         <v>91</v>
       </c>
       <c r="B30" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="18" thickBot="1">
@@ -1043,10 +1055,10 @@
         <v>91</v>
       </c>
       <c r="B31" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="18" thickBot="1">
@@ -1054,10 +1066,10 @@
         <v>91</v>
       </c>
       <c r="B32" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="18" thickBot="1">
@@ -1065,10 +1077,10 @@
         <v>91</v>
       </c>
       <c r="B33" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" thickBot="1">
@@ -1076,10 +1088,10 @@
         <v>91</v>
       </c>
       <c r="B34" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="18" thickBot="1">
@@ -1087,10 +1099,10 @@
         <v>91</v>
       </c>
       <c r="B35" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18" thickBot="1">
@@ -1098,10 +1110,10 @@
         <v>91</v>
       </c>
       <c r="B36" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18" thickBot="1">
@@ -1109,10 +1121,10 @@
         <v>91</v>
       </c>
       <c r="B37" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" thickBot="1">
@@ -1120,10 +1132,10 @@
         <v>91</v>
       </c>
       <c r="B38" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18" thickBot="1">
@@ -1131,10 +1143,10 @@
         <v>91</v>
       </c>
       <c r="B39" s="1">
-        <v>39</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>79</v>
+        <v>38</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18" thickBot="1">
@@ -1142,10 +1154,10 @@
         <v>91</v>
       </c>
       <c r="B40" s="1">
-        <v>40</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" thickBot="1">
@@ -1153,21 +1165,21 @@
         <v>91</v>
       </c>
       <c r="B41" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18" thickBot="1">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18" thickBot="1">
@@ -1175,10 +1187,10 @@
         <v>92</v>
       </c>
       <c r="B43" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="18" thickBot="1">
@@ -1186,10 +1198,10 @@
         <v>92</v>
       </c>
       <c r="B44" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="18" thickBot="1">
@@ -1197,10 +1209,10 @@
         <v>92</v>
       </c>
       <c r="B45" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="18" thickBot="1">
@@ -1208,10 +1220,10 @@
         <v>92</v>
       </c>
       <c r="B46" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="18" thickBot="1">
@@ -1219,10 +1231,10 @@
         <v>92</v>
       </c>
       <c r="B47" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" thickBot="1">
@@ -1230,10 +1242,10 @@
         <v>92</v>
       </c>
       <c r="B48" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="18" thickBot="1">
@@ -1241,10 +1253,10 @@
         <v>92</v>
       </c>
       <c r="B49" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="18" thickBot="1">
@@ -1252,10 +1264,10 @@
         <v>92</v>
       </c>
       <c r="B50" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="18" thickBot="1">
@@ -1263,10 +1275,10 @@
         <v>92</v>
       </c>
       <c r="B51" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="18" thickBot="1">
@@ -1274,10 +1286,10 @@
         <v>92</v>
       </c>
       <c r="B52" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="18" thickBot="1">
@@ -1285,10 +1297,10 @@
         <v>92</v>
       </c>
       <c r="B53" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="18" thickBot="1">
@@ -1296,21 +1308,21 @@
         <v>92</v>
       </c>
       <c r="B54" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="18" thickBot="1">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="18" thickBot="1">
@@ -1318,10 +1330,10 @@
         <v>93</v>
       </c>
       <c r="B56" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="18" thickBot="1">
@@ -1329,10 +1341,10 @@
         <v>93</v>
       </c>
       <c r="B57" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="18" thickBot="1">
@@ -1340,10 +1352,10 @@
         <v>93</v>
       </c>
       <c r="B58" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="18" thickBot="1">
@@ -1351,10 +1363,10 @@
         <v>93</v>
       </c>
       <c r="B59" s="1">
-        <v>59</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="18" thickBot="1">
@@ -1362,10 +1374,10 @@
         <v>93</v>
       </c>
       <c r="B60" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="18" thickBot="1">
@@ -1373,10 +1385,10 @@
         <v>93</v>
       </c>
       <c r="B61" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="18" thickBot="1">
@@ -1384,10 +1396,10 @@
         <v>93</v>
       </c>
       <c r="B62" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="18" thickBot="1">
@@ -1395,10 +1407,10 @@
         <v>93</v>
       </c>
       <c r="B63" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="18" thickBot="1">
@@ -1406,10 +1418,10 @@
         <v>93</v>
       </c>
       <c r="B64" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="18" thickBot="1">
@@ -1417,10 +1429,10 @@
         <v>93</v>
       </c>
       <c r="B65" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="18" thickBot="1">
@@ -1428,10 +1440,10 @@
         <v>93</v>
       </c>
       <c r="B66" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18" thickBot="1">
@@ -1439,21 +1451,21 @@
         <v>93</v>
       </c>
       <c r="B67" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="18" thickBot="1">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B68" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="18" thickBot="1">
@@ -1461,10 +1473,10 @@
         <v>94</v>
       </c>
       <c r="B69" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="18" thickBot="1">
@@ -1472,10 +1484,10 @@
         <v>94</v>
       </c>
       <c r="B70" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18" thickBot="1">
@@ -1483,10 +1495,10 @@
         <v>94</v>
       </c>
       <c r="B71" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18" thickBot="1">
@@ -1494,10 +1506,10 @@
         <v>94</v>
       </c>
       <c r="B72" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="18" thickBot="1">
@@ -1505,10 +1517,10 @@
         <v>94</v>
       </c>
       <c r="B73" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="18" thickBot="1">
@@ -1516,10 +1528,10 @@
         <v>94</v>
       </c>
       <c r="B74" s="1">
-        <v>74</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18" thickBot="1">
@@ -1527,10 +1539,10 @@
         <v>94</v>
       </c>
       <c r="B75" s="1">
-        <v>75</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="18" thickBot="1">
@@ -1538,10 +1550,10 @@
         <v>94</v>
       </c>
       <c r="B76" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="18" thickBot="1">
@@ -1549,10 +1561,10 @@
         <v>94</v>
       </c>
       <c r="B77" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="18" thickBot="1">
@@ -1560,10 +1572,10 @@
         <v>94</v>
       </c>
       <c r="B78" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="18" thickBot="1">
@@ -1571,10 +1583,10 @@
         <v>94</v>
       </c>
       <c r="B79" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="18" thickBot="1">
@@ -1582,9 +1594,20 @@
         <v>94</v>
       </c>
       <c r="B80" s="1">
+        <v>79</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="18" thickBot="1">
+      <c r="A81" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" s="1">
         <v>80</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C81" s="2" t="s">
         <v>78</v>
       </c>
     </row>
